--- a/template/THV_MAU_R1_BankKichBan.xlsx
+++ b/template/THV_MAU_R1_BankKichBan.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chú giải ký hiệu" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Phân loại 12 HT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Kịch bản MAU" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Chăm sóc nóng × giá trị" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cờ đỏ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tổng quan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chú giải ký hiệu" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Phân loại 12 HT" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Kịch bản MAU" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Chăm sóc nóng × giá trị" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -61,14 +62,14 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C11B26"/>
-      <sz val="11"/>
+      <color rgb="0016222E"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0016222E"/>
-      <sz val="10"/>
+      <color rgb="00C11B26"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="12">
@@ -155,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,8 +173,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -562,7 +566,265 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="54" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🚩 CỜ ĐỎ — ĐỌC TRƯỚC MỌI SHEET KHÁC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ca mang dấu hiệu cần bác sĩ đánh giá sớm. Có ca bị trấn an sai thì việc đầu tiên là gọi lại khách đó hôm nay, không phải đọc tiếp báo cáo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>🚩 CỜ ĐỎ — đọc trước mọi con số khác</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>STT HT</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Tên KH</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Mã CĐ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Dấu hiệu</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Có SĐT</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Phụ trách</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>NV có trấn an sai?</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>L-code</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Việc phải làm ngay</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Phạm Văn Đức</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>CĐ-1</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Xuất huyết tiêu hóa</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Phạm Linh</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>CÓ: không sao đâu, chắc không sao, theo dõi thêm đã</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>L2.1</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>GỌI LẠI NGAY + rà soát lại hội thoại với trưởng nhóm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thị Hồng</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CĐ-6</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Tiền sử gia đình ung thư tiêu hóa</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thu</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>L4.1</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Gọi trong SLA ≤5' + chuyển bác sĩ trong ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Lý Thị Oanh</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>CĐ-2</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Sụt cân nhanh không rõ lý do</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Ngô Hà</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>L4.1</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Gọi trong SLA ≤5' + chuyển bác sĩ trong ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Tỷ lệ xử lý đúng: 2/3 ca. MỐC LÀ 100% — đây là mốc duy nhất của hệ này không thương lượng. Dưới 100% thì xử lý trước khi hết kỳ, không chờ báo cáo sau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>⚠ Script quét bằng từ khoá và nhận RỘNG: thà gắn thừa còn hơn bỏ sót. Danh sách này CẦN NGƯỜI ĐỌC LẠI. Lưu ý máu ĐỎ TƯƠI khi đi ngoài là TH-06, không phải cờ đỏ; PHÂN ĐEN thì là cờ đỏ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>⚠ Script quét bằng từ khoá nên chỉ gợi ý. Người đọc lại từng ca mới là nguồn chốt — đặc biệt với ca nhân viên CÓ nhận ra nhưng xử lý nửa vời.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -570,10 +832,6 @@
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="53" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="54" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -594,451 +852,374 @@
       <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>🚩 CỜ ĐỎ — đọc trước mọi con số khác</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>🚩 CỜ ĐỎ</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>3 ca có dấu hiệu cần khám sớm, trong đó 1 ca bị nhân viên trấn an sai. Chi tiết ở sheet "Cờ đỏ" — đọc sheet đó trước sheet này.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>STT HT</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Tên KH</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Mã CĐ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Dấu hiệu</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Có SĐT</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Phụ trách</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>NV có trấn an sai?</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>L-code</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Việc phải làm ngay</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Phạm Văn Đức</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>CĐ-1</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Xuất huyết tiêu hóa</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Phạm Linh</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>CÓ: không sao đâu, chắc không sao, theo dõi thêm đã</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L2.1</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>GỌI LẠI NGAY + rà soát lại hội thoại với trưởng nhóm</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Trần Thị Hồng</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>CĐ-6</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Tiền sử gia đình ung thư tiêu hóa</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Trần Thu</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>L4.1</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Gọi trong SLA ≤5' + chuyển bác sĩ trong ngày</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>⚠ CẢNH BÁO PHƯƠNG PHÁP — đọc trước khi dùng số</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Lý Thị Oanh</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>CĐ-2</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Sụt cân nhanh không rõ lý do</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Ngô Hà</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>L4.1</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Gọi trong SLA ≤5' + chuyển bác sĩ trong ngày</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>• Mẫu: 12 hội thoại. ⚠ Người lập báo cáo phải xác nhận đây là TOÀN BỘ hội thoại trong kỳ, hay đã lọc (theo độ dài / theo có số điện thoại).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>• 7 nhóm vấn đề có dưới 10 hội thoại → ⚠ chưa đủ mẫu, không xếp hạng, không khuyến nghị.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Tỷ lệ xử lý đúng: 2/3 ca. MỐC LÀ 100% — đây là mốc duy nhất của hệ này không thương lượng. Dưới 100% thì xử lý trước khi hết kỳ, không chờ báo cáo sau.</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>• 🚩 3 ca có dấu hiệu CỜ ĐỎ trong kỳ. Luật ghi đè đẩy mọi ca này lên HOT, nên % HOT của bảng chia nhóm KHÔNG nói về chất lượng quảng cáo — đọc cột đã trừ cờ đỏ, và tách TH-01 ra khỏi mọi so sánh.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>⚠ Script quét bằng từ khoá và nhận RỘNG: thà gắn thừa còn hơn bỏ sót. Danh sách này CẦN NGƯỜI ĐỌC LẠI. Lưu ý máu ĐỎ TƯƠI khi đi ngoài là TH-06, không phải cờ đỏ; PHÂN ĐEN thì là cờ đỏ.</t>
+          <t>• 🚩 Danh sách cờ đỏ do script quét bằng TỪ KHOÁ và nhận RỘNG. Đây là danh sách CẦN NGƯỜI ĐỌC LẠI, không phải kết luận y khoa.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>• Mọi con số giá/ưu đãi trong file đều phải đối chiếu P7 bản hiện hành. Số nào trích từ hội thoại thì là 'nhân viên đã nói với khách', không phải giá chính thức. Giá của THV thay đổi theo NGƯỜI THỰC HIỆN và theo có tiền mê hay không.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>• Phễu có BA con số ở cuối: đặt lịch → đến khám → SOI ĐƯỢC. Chưa có số thì ghi ⚠ chưa đo được. Không lấy 'đặt lịch' thay cho 'đến khám', không lấy 'đến khám' thay cho 'soi được'.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>⚠ CẢNH BÁO PHƯƠNG PHÁP — đọc trước khi dùng số</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>• Mẫu: 12 hội thoại. ⚠ Người lập báo cáo phải xác nhận đây là TOÀN BỘ hội thoại trong kỳ, hay đã lọc (theo độ dài / theo có số điện thoại).</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Kết quả phân loại — đếm thật từ dữ liệu</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>• 7 nhóm vấn đề có dưới 10 hội thoại → ⚠ chưa đủ mẫu, không xếp hạng, không khuyến nghị.</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Số</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>• 🚩 3 ca có dấu hiệu CỜ ĐỎ trong kỳ. Luật ghi đè đẩy mọi ca này lên HOT, nên % HOT của bảng chia nhóm KHÔNG nói về chất lượng quảng cáo — đọc cột đã trừ cờ đỏ, và tách TH-01 ra khỏi mọi so sánh.</t>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Tổng hội thoại</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>• 🚩 Danh sách cờ đỏ do script quét bằng TỪ KHOÁ và nhận RỘNG. Đây là danh sách CẦN NGƯỜI ĐỌC LẠI, không phải kết luận y khoa.</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Có SĐT</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>• Mọi con số giá/ưu đãi trong file đều phải đối chiếu P7 bản hiện hành. Số nào trích từ hội thoại thì là 'nhân viên đã nói với khách', không phải giá chính thức. Giá của THV thay đổi theo NGƯỜI THỰC HIỆN và theo có tiền mê hay không.</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Không có SĐT</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>• Phễu có BA con số ở cuối: đặt lịch → đến khám → SOI ĐƯỢC. Chưa có số thì ghi ⚠ chưa đo được. Không lấy 'đặt lịch' thay cho 'đến khám', không lấy 'đến khám' thay cho 'soi được'.</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Độ nóng</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Số</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả phân loại — đếm thật từ dữ liệu</t>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>trong đó 6 ca do luật ghi đè</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ số</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Số</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Tổng hội thoại</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>COLD</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Có SĐT</t>
+          <t xml:space="preserve">   ghi đè: đã đặt lịch</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>41,7%</t>
-        </is>
-      </c>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Không có SĐT</t>
+          <t xml:space="preserve">   ghi đè: 🚩 cờ đỏ</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>58,3%</t>
-        </is>
-      </c>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ghi đè: đã có kết quả nơi khác</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Độ nóng</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ghi đè: đến hẹn soi lại</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm giá trị</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Số</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>HOT</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>trong đó 6 ca do luật ghi đè</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>WARM</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Nghĩa</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>COLD</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr"/>
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Combo dạ dày + đại tràng · can thiệp (cắt polyp, cầm máu) · gói tầm soát</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ghi đè: đã đặt lịch</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>41,7%</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Soi dạ dày HOẶC đại tràng đơn lẻ · soi + test HP</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ghi đè: 🚩 cờ đỏ</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr"/>
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>Khám chuyên khoa · trực tràng · sigma · siêu âm · test HP</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ghi đè: đã có kết quả nơi khác</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
@@ -1049,23 +1230,25 @@
           <t>8,3%</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Chưa xác định được — thường là TH-12 hỏi chung</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ghi đè: đến hẹn soi lại</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr"/>
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>⚠ Lưu ý khi đọc</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr"/>
+      <c r="C35" s="6" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Một lead WARM của combo tầm soát (WARM·G1) đáng đầu tư hơn một lead HOT của khám đầy hơi (HOT·G3) — dải giá chênh gần chín lần. Không xếp hạng lead chỉ bằng độ nóng.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -1073,369 +1256,365 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Nhóm giá trị</t>
+          <t>Nhóm vấn đề</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Tên nhóm</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
           <t>Số</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Nghĩa</t>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Đủ mẫu?</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="n">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>TH-01</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>🚩 CỜ ĐỎ — dấu hiệu cần khám ngay</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>TH-02</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>Theo dõi sau can thiệp · đến hẹn soi lại</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>TH-04</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Dạ dày – thực quản</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>TH-05</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>Đại tràng – trực tràng</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>TH-06</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>Chảy máu thấp · trĩ – hậu môn</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>TH-09</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>Rối loạn tiêu hóa chung</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>TH-12</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Chưa rõ / hỏi chung</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Giai đoạn</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Số</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>Combo dạ dày + đại tràng · can thiệp (cắt polyp, cầm máu) · gói tầm soát</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="n">
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>41,7%</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>Soi dạ dày HOẶC đại tràng đơn lẻ · soi + test HP</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n">
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>16,7%</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>Khám chuyên khoa · trực tràng · sigma · siêu âm · test HP</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Chưa xác định được — thường là TH-12 hỏi chung</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>⚠ Lưu ý khi đọc</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr"/>
-      <c r="C42" s="6" t="inlineStr"/>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Một lead WARM của combo tầm soát (WARM·G1) đáng đầu tư hơn một lead HOT của khám đầy hơi (HOT·G3) — dải giá chênh gần chín lần. Không xếp hạng lead chỉ bằng độ nóng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Nhóm vấn đề</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Tên nhóm</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Số</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Đủ mẫu?</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>TH-01</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>🚩 CỜ ĐỎ — dấu hiệu cần khám ngay</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="n">
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Rào cản</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Số lượt</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>% trên tổng HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>L6.7 Ngại tiền mê / gây mê</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>SỢ</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>TH-02</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>Theo dõi sau can thiệp · đến hẹn soi lại</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>TH-04</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>Dạ dày – thực quản</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>TH-05</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>Đại tràng – trực tràng</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>TH-06</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>Chảy máu thấp · trĩ – hậu môn</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>TH-09</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>Rối loạn tiêu hóa chung</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>TH-12</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>Chưa rõ / hỏi chung</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Giai đoạn</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Số</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B54" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C54" s="14" t="inlineStr">
-        <is>
-          <t>33,3%</t>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>L6.5 Sợ nội soi</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>SỢ</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="n">
+          <t>L6.9 Ngờ vệ sinh dây soi</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>NGỜ</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
@@ -1444,167 +1623,158 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>41,7%</t>
+          <t>L6.8 Né kết quả</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>NÉ</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>16,7%</t>
+          <t>L6.3 Chưa tài chính / hỏi bảo hiểm</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>NGẠI</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>L6.6 Hỏi ý kiến người thân</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>NGỜ+NGẠI</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Rào cản</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>L6.2 So sánh nơi khác</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>NGỜ</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>⚠ Cách đếm</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr"/>
+      <c r="C60" s="6" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Một hội thoại có thể mang nhiều rào cản → tổng lượt LỚN HƠN tổng hội thoại là đúng, không phải lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Nhóm đối tượng theo insight</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Nhóm</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Số lượt</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>% trên tổng HT</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>L6.7 Ngại tiền mê / gây mê</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>SỢ</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>L6.5 Sợ nội soi</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>SỢ</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>L6.9 Ngờ vệ sinh dây soi</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>NGỜ</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>L6.8 Né kết quả</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>NÉ</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>8,3%</t>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Số HT</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Insight / nỗi lo thật</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>L6.3 Chưa tài chính / hỏi bảo hiểm</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>NGẠI</t>
+          <t>Z 🚩 CA CỜ ĐỎ — xử lý trước mọi nhóm</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>🚩 Có phải bệnh nặng không — XỬ LÝ TRƯỚC MỌI NHÓM, gọi ≤5' và chuyển bác sĩ trong ngày</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>L6.6 Hỏi ý kiến người thân</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>NGỜ+NGẠI</t>
+          <t>A1 hỏi giá ngay chưa kể triệu chứng</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
@@ -1612,145 +1782,179 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>Chưa kể triệu chứng, hỏi giá để sàng lọc nhanh</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>L6.2 So sánh nơi khác</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>NGỜ</t>
+          <t>A2 triệu chứng dai dẳng, đã tự uống thuốc</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Uống thuốc mãi không khỏi, có phải bị nặng rồi không</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>A3 tầm soát chủ động / chưa có triệu chứng</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có triệu chứng thì có cần soi không · bao lâu soi lại một lần — nhóm GIÁ TRỊ CAO NHẤT mà ít bị chấm HOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>A4 sợ nội soi hoặc ngại tiền mê</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>⚠ Cách đếm</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr"/>
-      <c r="C67" s="6" t="inlineStr"/>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Một hội thoại có thể mang nhiều rào cản → tổng lượt LỚN HƠN tổng hội thoại là đúng, không phải lỗi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Tôi có chịu được không · thuốc mê có hại không · các anh có nói thật không</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Nhóm đối tượng theo insight</t>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>A5 ở xa Hà Nội</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Lên Hà Nội một buổi có xong việc không</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Nhóm</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>Số HT</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>Insight / nỗi lo thật</t>
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>A6 mang kết quả nơi khác đến</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Kết quả này nghĩa là gì · có phải soi lại không</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Z 🚩 CA CỜ ĐỎ — xử lý trước mọi nhóm</t>
+          <t>A7 né kết quả (L6.8)</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>🚩 Có phải bệnh nặng không — XỬ LÝ TRƯỚC MỌI NHÓM, gọi ≤5' và chuyển bác sĩ trong ngày</t>
+          <t>Tôi sợ chính cái kết quả, không sợ ống soi — ⛔ gửi ưu đãi cho nhóm này là đẩy họ xa thêm</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>A1 hỏi giá ngay chưa kể triệu chứng</t>
+          <t>B1 vừa cho số</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Chưa kể triệu chứng, hỏi giá để sàng lọc nhanh</t>
+          <t>Vừa cho số, đang chờ được gọi — rơi ở đây là đắt nhất</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>A2 triệu chứng dai dẳng, đã tự uống thuốc</t>
+          <t>B2 chưa kết nối được</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Uống thuốc mãi không khỏi, có phải bị nặng rồi không</t>
+          <t>Đã cho số mà không gọi được</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>A3 tầm soát chủ động / chưa có triệu chứng</t>
+          <t>B3 chỉ nhắn Zalo</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
@@ -1758,59 +1962,59 @@
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Chưa có triệu chứng thì có cần soi không · bao lâu soi lại một lần — nhóm GIÁ TRỊ CAO NHẤT mà ít bị chấm HOT</t>
+          <t>Không muốn nghe điện, chỉ nhắn</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>A4 sợ nội soi hoặc ngại tiền mê</t>
+          <t>B4 đã gọi còn rào cản</t>
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Tôi có chịu được không · thuốc mê có hại không · các anh có nói thật không</t>
+          <t>Đã nghe tư vấn, còn vướng một rào cản cụ thể</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>B5</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>A5 ở xa Hà Nội</t>
+          <t>B5 đã đặt lịch — CẦN DẶN CHUẨN BỊ</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Lên Hà Nội một buổi có xong việc không</t>
+          <t>Đã có lịch — CẦN DẶN CHUẨN BỊ để soi được luôn trong buổi đó</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>A6 mang kết quả nơi khác đến</t>
+          <t>C1 vừa soi xong / đang theo dõi</t>
         </is>
       </c>
       <c r="C77" s="6" t="n">
@@ -1818,39 +2022,39 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Kết quả này nghĩa là gì · có phải soi lại không</t>
+          <t>Lo kết quả, chế độ ăn, dùng thuốc theo đơn</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>A7 né kết quả (L6.8)</t>
+          <t>C2 đến hẹn soi lại</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Tôi sợ chính cái kết quả, không sợ ống soi — ⛔ gửi ưu đãi cho nhóm này là đẩy họ xa thêm</t>
+          <t>Đến hẹn soi lại — tệp gần như chắc chắn quay lại nếu được nhắc đúng mốc trong phiếu kết quả</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>B1 vừa cho số</t>
+          <t>C3 giới thiệu người nhà</t>
         </is>
       </c>
       <c r="C79" s="6" t="n">
@@ -1858,189 +2062,185 @@
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Vừa cho số, đang chờ được gọi — rơi ở đây là đắt nhất</t>
+          <t>Hài lòng → giới thiệu người nhà cùng tầm soát</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>B2 chưa kết nối được</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>Đã cho số mà không gọi được</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>B3 chỉ nhắn Zalo</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>Không muốn nghe điện, chỉ nhắn</t>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Lỗi quan sát trong data — phải tránh</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>B4 đã gọi còn rào cản</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>Đã nghe tư vấn, còn vướng một rào cản cụ thể</t>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Lỗi</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Số HT phát hiện</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Dẫn chứng (số hiệu HT)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
+      <c r="A83" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>B5 đã đặt lịch — CẦN DẶN CHUẨN BỊ</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="n">
+          <t>Lờ câu hỏi giá — khách hỏi giá, nhân viên chỉ đáp "để lại số"</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đo được</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>⚠ cần đọc hiểu, script không bắt được — xem R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>🚩 Trấn an một ca có cờ đỏ — lỗi nặng nhất của hệ</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>Đã có lịch — CẦN DẶN CHUẨN BỊ để soi được luôn trong buổi đó</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>C1 vừa soi xong / đang theo dõi</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>Lo kết quả, chế độ ăn, dùng thuốc theo đơn</t>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>HT#4</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
+      <c r="A85" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>C2 đến hẹn soi lại</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="n">
+          <t>Chẩn đoán hoặc loại trừ bệnh qua tin nhắn</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đo được</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>⚠ cần đọc hiểu — xem R3 sheet Rủi ro pháp lý</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Đọc kết quả nội soi / xét nghiệm / giải phẫu bệnh qua inbox</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đo được</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>⚠ cần đọc hiểu — xem R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Tư vấn thuốc, liều, phác đồ — kể cả phác đồ diệt HP</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đo được</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>⚠ cần đọc hiểu — xem R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Nói "không đau" / dùng từ cấm</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>Đến hẹn soi lại — tệp gần như chắc chắn quay lại nếu được nhắc đúng mốc trong phiếu kết quả</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>C3 giới thiệu người nhà</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>Hài lòng → giới thiệu người nhà cùng tầm soát</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>Lỗi quan sát trong data — phải tránh</t>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>HT#4, HT#12</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Lỗi</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>Số HT phát hiện</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>Dẫn chứng (số hiệu HT)</t>
+      <c r="A89" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Hứa chắc tiền mê được khi chưa biết bệnh nền</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đo được</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>⚠ cần đọc hiểu — xem R3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Lờ câu hỏi giá — khách hỏi giá, nhân viên chỉ đáp "để lại số"</t>
+          <t>Báo giá mà không nói 3 điều kiện (ai thực hiện · có tiền mê · phụ phí)</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
@@ -2050,17 +2250,17 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>⚠ cần đọc hiểu, script không bắt được — xem R3</t>
+          <t>⚠ cần đọc hiểu — xem R3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Bắn giá cứng cho một ca cụ thể</t>
+          <t>Xin số không có lý do, hoặc lý do "để gửi ưu đãi"</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -2076,11 +2276,11 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Dán mẫu máy móc, trả lời không dính điều khách vừa nói</t>
+          <t>Mời khám mà KHÔNG dặn chuẩn bị · xin số rồi để yên</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
@@ -2096,147 +2296,49 @@
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>BỎ MẤT BẰNG CHỨNG: khách nêu rào cản mà NV không đưa bằng chứng nào</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Nói "không đau" / dùng từ cấm</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>HT#4, HT#12</t>
+          <t>HT#6, HT#7, HT#8, HT#9</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Gắn "chính hãng" cho vật liệu ngoài 4 hãng đã duyệt</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>⚠ chưa đo được</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>⚠ cần đọc hiểu — xem R3 sheet Rủi ro pháp lý</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Xin số không có lý do, hoặc lý do "để gửi ưu đãi"</t>
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>⚠ BIẾN SỐ TỪ CHƯƠNG TRÌNH THÁNG</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>⚠ Cần xác minh từ THV</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>⚠ chưa đo được</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>⚠ cần đọc hiểu — xem R3</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>Xin số rồi để yên — không nhắn xác nhận ai gọi, số nào, mấy giờ</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>⚠ chưa đo được</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>⚠ cần đọc hiểu — xem R3</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>Hứa thời gian điều trị cứng</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>⚠ chưa đo được</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>⚠ cần đọc hiểu — xem R3</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>BỎ MẤT BẰNG CHỨNG: khách ngờ vật liệu (L6.7) mà không nhắc đối tác hãng</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>HT#6, HT#7, HT#8, HT#9</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>⚠ BIẾN SỐ TỪ CHƯƠNG TRÌNH THÁNG</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>⚠ Cần xác minh từ THV</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
           <t>P7 chưa điền → mọi ưu đãi/giá/% /trả góp trong nội dung gợi ý để dạng {biến} kèm ⚠, trực page tự điền theo P7 hiện hành.</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr"/>
+      <c r="D95" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2697,7 +2799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2847,7 +2949,7 @@
           <t>L4.1</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>HOT</t>
         </is>
@@ -2910,7 +3012,7 @@
           <t>L2.1</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>COLD</t>
         </is>
@@ -2973,7 +3075,7 @@
           <t>L4.1</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>HOT</t>
         </is>
@@ -3036,7 +3138,7 @@
           <t>L2.1</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>HOT</t>
         </is>
@@ -3099,7 +3201,7 @@
           <t>L6.7</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>COLD</t>
         </is>
@@ -3162,7 +3264,7 @@
           <t>L4.1</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>HOT</t>
         </is>
@@ -3225,7 +3327,7 @@
           <t>L6.8</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>COLD</t>
         </is>
@@ -3288,7 +3390,7 @@
           <t>L6.3</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>WARM</t>
         </is>
@@ -3351,7 +3453,7 @@
           <t>L4.1</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>HOT</t>
         </is>
@@ -3414,7 +3516,7 @@
           <t>L6.2</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>WARM</t>
         </is>
@@ -3477,7 +3579,7 @@
           <t>L4.1</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>HOT</t>
         </is>
@@ -3540,7 +3642,7 @@
           <t>L2.1</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>WARM</t>
         </is>
@@ -3566,7 +3668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3669,17 +3771,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>S1 · S3</t>
         </is>
@@ -3689,17 +3791,17 @@
           <t>⚠ viết lại theo lời khách thật trong 3 ca của nhóm này</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>L6.7 Ngại tiền mê / gây mê</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>L2.1 · L4.1</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>G1(3)</t>
         </is>
@@ -3709,7 +3811,7 @@
           <t>3 ca trong kỳ · ⚠ chưa đủ mẫu</t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Dạ với [bệnh nền anh/chị vừa kể] thì bác sĩ phải khám sàng lọc trước mới quyết định được có tiền mê hay không, em chưa dám hứa trước ạ. Khi làm tiền mê thì có bác sĩ gây mê theo dõi riêng trong suốt ca soi.
 Anh/chị tiện [sáng mai] hay [Chủ nhật này] để bác sĩ khám và đánh giá ạ?</t>
@@ -3725,24 +3827,24 @@
           <t>⚠ chưa viết — nội dung chạm lần 3</t>
         </is>
       </c>
-      <c r="L5" s="16" t="inlineStr">
-        <is>
-          <t>Không từ cấm · "chính hãng" chỉ cho 4 hãng duyệt · không chốt giá ca cụ thể · không hứa thời gian cứng · không chẩn đoán qua tin nhắn</t>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t>Không từ cấm · không chẩn đoán / loại trừ bệnh · không đọc kết quả · không tư vấn thuốc · không hứa chắc tiền mê · nêu khung giá phải kèm 3 điều kiện · ca cờ đỏ thì KHÔNG nêu giá, KHÔNG trấn an</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
@@ -3752,17 +3854,17 @@
           <t>⚠ viết lại theo lời khách thật trong 1 ca của nhóm này</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>— chưa xác định</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>L2.1</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>?(1)</t>
         </is>
@@ -3789,24 +3891,24 @@
           <t>⚠ chưa viết — nội dung chạm lần 3</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>Không từ cấm · "chính hãng" chỉ cho 4 hãng duyệt · không chốt giá ca cụ thể · không hứa thời gian cứng · không chẩn đoán qua tin nhắn</t>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t>Không từ cấm · không chẩn đoán / loại trừ bệnh · không đọc kết quả · không tư vấn thuốc · không hứa chắc tiền mê · nêu khung giá phải kèm 3 điều kiện · ca cờ đỏ thì KHÔNG nêu giá, KHÔNG trấn an</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>S1 · S3</t>
         </is>
@@ -3816,17 +3918,17 @@
           <t>⚠ viết lại theo lời khách thật trong 3 ca của nhóm này</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>L6.3 Chưa tài chính / hỏi bảo hiểm</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>L2.1 · L6.2 · L6.3</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>G2(3)</t>
         </is>
@@ -3853,24 +3955,24 @@
           <t>⚠ chưa viết — nội dung chạm lần 3</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>Không từ cấm · "chính hãng" chỉ cho 4 hãng duyệt · không chốt giá ca cụ thể · không hứa thời gian cứng · không chẩn đoán qua tin nhắn</t>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t>Không từ cấm · không chẩn đoán / loại trừ bệnh · không đọc kết quả · không tư vấn thuốc · không hứa chắc tiền mê · nêu khung giá phải kèm 3 điều kiện · ca cờ đỏ thì KHÔNG nêu giá, KHÔNG trấn an</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3880,22 +3982,22 @@
           <t>⚠ chưa có ca trong kỳ này</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3905,22 +4007,22 @@
           <t>⚠ chưa viết — không có ca để căn cứ</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="16" t="inlineStr"/>
-      <c r="L8" s="16" t="inlineStr"/>
+      <c r="J8" s="17" t="inlineStr"/>
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3930,17 +4032,17 @@
           <t>⚠ viết lại theo lời khách thật trong 1 ca của nhóm này</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>L6.7 Ngại tiền mê / gây mê</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>L6.7</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>G3(1)</t>
         </is>
@@ -3950,7 +4052,7 @@
           <t>1 ca trong kỳ · ⚠ chưa đủ mẫu</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Dạ với [bệnh nền anh/chị vừa kể] thì bác sĩ phải khám sàng lọc trước mới quyết định được có tiền mê hay không, em chưa dám hứa trước ạ. Khi làm tiền mê thì có bác sĩ gây mê theo dõi riêng trong suốt ca soi.
 Anh/chị tiện [sáng mai] hay [Chủ nhật này] để bác sĩ khám và đánh giá ạ?</t>
@@ -3966,24 +4068,24 @@
           <t>⚠ chưa viết — nội dung chạm lần 3</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>Không từ cấm · "chính hãng" chỉ cho 4 hãng duyệt · không chốt giá ca cụ thể · không hứa thời gian cứng · không chẩn đoán qua tin nhắn</t>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>Không từ cấm · không chẩn đoán / loại trừ bệnh · không đọc kết quả · không tư vấn thuốc · không hứa chắc tiền mê · nêu khung giá phải kèm 3 điều kiện · ca cờ đỏ thì KHÔNG nêu giá, KHÔNG trấn an</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>A5</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>A5</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3993,22 +4095,22 @@
           <t>⚠ chưa có ca trong kỳ này</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4018,22 +4120,22 @@
           <t>⚠ chưa viết — không có ca để căn cứ</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="16" t="inlineStr"/>
-      <c r="L10" s="16" t="inlineStr"/>
+      <c r="J10" s="17" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr"/>
+      <c r="L10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>A6</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>A6</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4043,22 +4145,22 @@
           <t>⚠ chưa có ca trong kỳ này</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4068,22 +4170,22 @@
           <t>⚠ chưa viết — không có ca để căn cứ</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr"/>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr"/>
+      <c r="J11" s="17" t="inlineStr"/>
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>A7</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>A7</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4093,17 +4195,17 @@
           <t>⚠ viết lại theo lời khách thật trong 1 ca của nhóm này</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>L6.8 Né kết quả</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>L6.8</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>G3(1)</t>
         </is>
@@ -4113,7 +4215,7 @@
           <t>1 ca trong kỳ · ⚠ chưa đủ mẫu</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Dạ em hiểu ạ. Phần lớn tổn thương phát hiện sớm thì xử lý được, có những tổn thương nhỏ bác sĩ xử lý ngay trong lúc soi. Biết sớm là để chủ động, anh/chị ạ.
 Em giữ giúp anh/chị buổi [Chủ nhật tuần sau] nhé, đổi được nếu anh/chị có việc.
@@ -4130,24 +4232,24 @@
           <t>⚠ chưa viết — nội dung chạm lần 3</t>
         </is>
       </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>Không từ cấm · "chính hãng" chỉ cho 4 hãng duyệt · không chốt giá ca cụ thể · không hứa thời gian cứng · không chẩn đoán qua tin nhắn</t>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>Không từ cấm · không chẩn đoán / loại trừ bệnh · không đọc kết quả · không tư vấn thuốc · không hứa chắc tiền mê · nêu khung giá phải kèm 3 điều kiện · ca cờ đỏ thì KHÔNG nêu giá, KHÔNG trấn an</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4157,22 +4259,22 @@
           <t>⚠ chưa có ca trong kỳ này</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4182,22 +4284,22 @@
           <t>⚠ chưa viết — không có ca để căn cứ</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr"/>
+      <c r="J13" s="17" t="inlineStr"/>
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4207,22 +4309,22 @@
           <t>⚠ chưa có ca trong kỳ này</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4232,22 +4334,22 @@
           <t>⚠ chưa viết — không có ca để căn cứ</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr"/>
-      <c r="K14" s="16" t="inlineStr"/>
-      <c r="L14" s="16" t="inlineStr"/>
+      <c r="J14" s="17" t="inlineStr"/>
+      <c r="K14" s="17" t="inlineStr"/>
+      <c r="L14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4257,22 +4359,22 @@
           <t>⚠ chưa có ca trong kỳ này</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4282,22 +4384,22 @@
           <t>⚠ chưa viết — không có ca để căn cứ</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr"/>
+      <c r="J15" s="17" t="inlineStr"/>
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4307,22 +4409,22 @@
           <t>⚠ chưa có ca trong kỳ này</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4332,22 +4434,22 @@
           <t>⚠ chưa viết — không có ca để căn cứ</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="16" t="inlineStr"/>
+      <c r="J16" s="17" t="inlineStr"/>
+      <c r="K16" s="17" t="inlineStr"/>
+      <c r="L16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4357,17 +4459,17 @@
           <t>⚠ viết lại theo lời khách thật trong 1 ca của nhóm này</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>— chưa xác định</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>L4.1</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>G2(1)</t>
         </is>
@@ -4394,24 +4496,24 @@
           <t>⚠ chưa viết — nội dung chạm lần 3</t>
         </is>
       </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>Không từ cấm · "chính hãng" chỉ cho 4 hãng duyệt · không chốt giá ca cụ thể · không hứa thời gian cứng · không chẩn đoán qua tin nhắn</t>
+      <c r="L17" s="17" t="inlineStr">
+        <is>
+          <t>Không từ cấm · không chẩn đoán / loại trừ bệnh · không đọc kết quả · không tư vấn thuốc · không hứa chắc tiền mê · nêu khung giá phải kèm 3 điều kiện · ca cờ đỏ thì KHÔNG nêu giá, KHÔNG trấn an</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4421,22 +4523,22 @@
           <t>⚠ chưa có ca trong kỳ này</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4446,22 +4548,22 @@
           <t>⚠ chưa viết — không có ca để căn cứ</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
-      <c r="L18" s="16" t="inlineStr"/>
+      <c r="J18" s="17" t="inlineStr"/>
+      <c r="K18" s="17" t="inlineStr"/>
+      <c r="L18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -4471,17 +4573,17 @@
           <t>⚠ viết lại theo lời khách thật trong 2 ca của nhóm này</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>L6.5 Sợ nội soi (nôn, sặc, đau)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>L4.1</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>G2(1) · G1(1)</t>
         </is>
@@ -4491,7 +4593,7 @@
           <t>2 ca trong kỳ · ⚠ chưa đủ mẫu</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>Dạ em nói thật với anh/chị: soi thường có cảm giác khó chịu, không phải không có. Còn bản tiền mê thì anh/chị ngủ trong lúc soi, có bác sĩ gây mê theo dõi riêng ạ.
 Anh/chị đến khám trước đã, bác sĩ xem rồi mới quyết định có cần soi và soi loại nào. Anh/chị tiện [khung giờ 1] hay [khung giờ 2] ạ?</t>
@@ -4507,24 +4609,24 @@
           <t>⚠ chưa viết — nội dung chạm lần 3</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>Không từ cấm · "chính hãng" chỉ cho 4 hãng duyệt · không chốt giá ca cụ thể · không hứa thời gian cứng · không chẩn đoán qua tin nhắn</t>
+      <c r="L19" s="17" t="inlineStr">
+        <is>
+          <t>Không từ cấm · không chẩn đoán / loại trừ bệnh · không đọc kết quả · không tư vấn thuốc · không hứa chắc tiền mê · nêu khung giá phải kèm 3 điều kiện · ca cờ đỏ thì KHÔNG nêu giá, KHÔNG trấn an</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4534,22 +4636,22 @@
           <t>⚠ chưa có ca trong kỳ này</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4559,16 +4661,16 @@
           <t>⚠ chưa viết — không có ca để căn cứ</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr"/>
-      <c r="K20" s="16" t="inlineStr"/>
-      <c r="L20" s="16" t="inlineStr"/>
+      <c r="J20" s="17" t="inlineStr"/>
+      <c r="K20" s="17" t="inlineStr"/>
+      <c r="L20" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4653,7 +4755,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>HOT</t>
         </is>
@@ -4698,7 +4800,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>HOT</t>
         </is>
@@ -4743,7 +4845,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>HOT</t>
         </is>
@@ -4788,7 +4890,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>WARM</t>
         </is>
@@ -4833,7 +4935,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>WARM</t>
         </is>
@@ -4878,7 +4980,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>WARM</t>
         </is>
@@ -4923,7 +5025,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>COLD</t>
         </is>
@@ -4968,7 +5070,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>COLD</t>
         </is>
@@ -5013,7 +5115,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>COLD</t>
         </is>
@@ -5103,25 +5205,25 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>TỔNG</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="n">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Phải bằng tổng hội thoại đếm được ở sheet 1</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
